--- a/output/summary_tables/Permitting Module Summary Tables.xlsx
+++ b/output/summary_tables/Permitting Module Summary Tables.xlsx
@@ -8,16 +8,18 @@
   <sheets>
     <sheet name="Categorical" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Quantitative" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Dummy" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="165" formatCode="0.0"/>
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="168" formatCode="yyyy-mm-dd"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -38,7 +40,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -58,6 +60,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFA6C9EC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFD966"/>
       </patternFill>
     </fill>
   </fills>
@@ -87,7 +94,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf applyBorder="1" borderId="1" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
     <xf applyBorder="1" applyFont="1" borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0"/>
@@ -122,10 +129,21 @@
     <xf applyBorder="1" applyFont="1" applyNumberFormat="1" borderId="1" fillId="0" fontId="1" numFmtId="14" xfId="0"/>
     <xf applyBorder="1" applyFill="1" applyFont="1" borderId="1" fillId="4" fontId="1" numFmtId="0" xfId="0"/>
     <xf applyBorder="1" applyFont="1" applyNumberFormat="1" borderId="1" fillId="0" fontId="1" numFmtId="167" xfId="0"/>
+    <xf applyBorder="1" applyFont="1" applyNumberFormat="1" borderId="1" fillId="0" fontId="1" numFmtId="168" xfId="0"/>
     <xf applyBorder="1" applyFill="1" applyFont="1" borderId="1" fillId="4" fontId="1" numFmtId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf applyBorder="1" applyFont="1" applyNumberFormat="1" borderId="1" fillId="0" fontId="1" numFmtId="167" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf applyBorder="1" applyFont="1" applyNumberFormat="1" borderId="1" fillId="0" fontId="1" numFmtId="168" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf applyBorder="1" applyFont="1" applyNumberFormat="1" borderId="1" fillId="0" fontId="1" numFmtId="168" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf applyBorder="1" applyFill="1" applyFont="1" borderId="1" fillId="5" fontId="1" numFmtId="0" xfId="0"/>
+    <xf applyBorder="1" applyFill="1" applyFont="1" borderId="1" fillId="5" fontId="1" numFmtId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -453,7 +471,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:F59"/>
+  <dimension ref="A1:F120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="28.5"/>
@@ -467,7 +485,7 @@
     <row r="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>Permitting - events in issuing, modifying, and renewing RCRA permits, mainly held by TSDFs.</t>
+          <t>Permitting - events in issuing, modifying, and renewing RCRA permits, mainly held by TSDFs. Summarized from the PM_MASTER master file.</t>
         </is>
       </c>
       <c r="B1" s="7"/>
@@ -479,7 +497,7 @@
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>Identifier: HANDLER_ID, one row per permit event.</t>
+          <t>Identifier: HANDLER_ID, one row per permit event x unit detail x waste code x subsequent-modification link.</t>
         </is>
       </c>
       <c r="B2" s="7"/>
@@ -495,7 +513,7 @@
         </is>
       </c>
       <c r="B3" s="7">
-        <v>283047</v>
+        <v>1606588</v>
       </c>
       <c r="C3" s="7" t="inlineStr">
         <is>
@@ -504,7 +522,7 @@
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>1980-01-11 to 2026-07-06</t>
+          <t>1980-01-11 to 2026-07-18</t>
         </is>
       </c>
       <c r="E3" s="7"/>
@@ -532,7 +550,7 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>2 other columns not summarized (identifiers, names, and descriptions / free-text fields).</t>
+          <t>6 other columns are not summarized because they hold record identifiers, personal names and staff identifiers, correspondence addresses and contact details, free-text notes, or the description text paired with a code that is summarized here. They are named below the table.</t>
         </is>
       </c>
       <c r="C5" s="7"/>
@@ -581,7 +599,7 @@
               <color rgb="FF000000"/>
               <rFont val="Calibri"/>
             </rPr>
-            <t xml:space="preserve">EVENT_AGENCY
+            <t xml:space="preserve">EVENT_ACTIVITY_LOCATION
 </t>
           </r>
           <r>
@@ -590,7 +608,7 @@
               <color rgb="FF666666"/>
               <rFont val="Calibri"/>
             </rPr>
-            <t>Agency responsible for the permitting event.</t>
+            <t>State or territory whose implementing agency is responsible for the event.</t>
           </r>
         </is>
       </c>
@@ -601,18 +619,18 @@
         </is>
       </c>
       <c r="C7" s="11">
-        <v>4</v>
+        <v>59</v>
       </c>
       <c r="D7" s="10" t="inlineStr">
         <is>
-          <t>S - State</t>
+          <t>UT</t>
         </is>
       </c>
       <c r="E7" s="12">
-        <v>85.9</v>
+        <v>11.9</v>
       </c>
       <c r="F7" s="10">
-        <v>243148</v>
+        <v>191541</v>
       </c>
     </row>
     <row r="8">
@@ -621,14 +639,14 @@
       <c r="C8" s="11"/>
       <c r="D8" s="10" t="inlineStr">
         <is>
-          <t>E - EPA</t>
+          <t>WA</t>
         </is>
       </c>
       <c r="E8" s="12">
-        <v>13.2</v>
+        <v>9.6</v>
       </c>
       <c r="F8" s="10">
-        <v>37268</v>
+        <v>154583</v>
       </c>
     </row>
     <row r="9">
@@ -637,14 +655,14 @@
       <c r="C9" s="11"/>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>J - Joint with State Lead</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="E9" s="12">
-        <v>0.9</v>
+        <v>7.4</v>
       </c>
       <c r="F9" s="10">
-        <v>2569</v>
+        <v>118403</v>
       </c>
     </row>
     <row r="10">
@@ -653,57 +671,30 @@
       <c r="C10" s="11"/>
       <c r="D10" s="10" t="inlineStr">
         <is>
-          <t>P - Joint with EPA Lead</t>
+          <t>CO</t>
         </is>
       </c>
       <c r="E10" s="12">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="F10" s="10">
-        <v>62</v>
+        <v>115385</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <sz val="12"/>
-              <color rgb="FF000000"/>
-              <rFont val="Calibri"/>
-            </rPr>
-            <t xml:space="preserve">EVENT_ACTIVITY_LOCATION
-</t>
-          </r>
-          <r>
-            <rPr>
-              <sz val="12"/>
-              <color rgb="FF666666"/>
-              <rFont val="Calibri"/>
-            </rPr>
-            <t>State or territory whose implementing agency is responsible for the event.</t>
-          </r>
-        </is>
-      </c>
-      <c r="B11" s="11" t="inlineStr">
-        <is>
-          <t>0%
-(0)</t>
-        </is>
-      </c>
-      <c r="C11" s="11">
-        <v>59</v>
-      </c>
+      <c r="A11" s="10"/>
+      <c r="B11" s="11"/>
+      <c r="C11" s="11"/>
       <c r="D11" s="10" t="inlineStr">
         <is>
           <t>OH</t>
         </is>
       </c>
       <c r="E11" s="12">
-        <v>8.7</v>
+        <v>7.1</v>
       </c>
       <c r="F11" s="10">
-        <v>24545</v>
+        <v>113504</v>
       </c>
     </row>
     <row r="12">
@@ -712,30 +703,57 @@
       <c r="C12" s="11"/>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>TX</t>
+          <t>All Other (54)</t>
         </is>
       </c>
       <c r="E12" s="12">
-        <v>7.8</v>
+        <v>56.8</v>
       </c>
       <c r="F12" s="10">
-        <v>21951</v>
+        <v>913172</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="10"/>
-      <c r="B13" s="11"/>
-      <c r="C13" s="11"/>
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color rgb="FF000000"/>
+              <rFont val="Calibri"/>
+            </rPr>
+            <t xml:space="preserve">EVENT_AGENCY
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color rgb="FF666666"/>
+              <rFont val="Calibri"/>
+            </rPr>
+            <t>Agency responsible for the permitting event.</t>
+          </r>
+        </is>
+      </c>
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t>0%
+(0)</t>
+        </is>
+      </c>
+      <c r="C13" s="11">
+        <v>4</v>
+      </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>NC</t>
+          <t>S - State</t>
         </is>
       </c>
       <c r="E13" s="12">
-        <v>5.5</v>
+        <v>94</v>
       </c>
       <c r="F13" s="10">
-        <v>15497</v>
+        <v>1510745</v>
       </c>
     </row>
     <row r="14">
@@ -744,14 +762,14 @@
       <c r="C14" s="11"/>
       <c r="D14" s="10" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>E - EPA</t>
         </is>
       </c>
       <c r="E14" s="12">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="F14" s="10">
-        <v>14227</v>
+        <v>69005</v>
       </c>
     </row>
     <row r="15">
@@ -760,14 +778,14 @@
       <c r="C15" s="11"/>
       <c r="D15" s="10" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>J - Joint with State Lead</t>
         </is>
       </c>
       <c r="E15" s="12">
-        <v>4.9</v>
+        <v>1.7</v>
       </c>
       <c r="F15" s="10">
-        <v>13958</v>
+        <v>26662</v>
       </c>
     </row>
     <row r="16">
@@ -776,14 +794,14 @@
       <c r="C16" s="11"/>
       <c r="D16" s="10" t="inlineStr">
         <is>
-          <t>All Other (54)</t>
+          <t>P - Joint with EPA Lead</t>
         </is>
       </c>
       <c r="E16" s="12">
-        <v>68.1</v>
+        <v>0</v>
       </c>
       <c r="F16" s="10">
-        <v>192869</v>
+        <v>176</v>
       </c>
     </row>
     <row r="17">
@@ -823,10 +841,10 @@
         </is>
       </c>
       <c r="E17" s="12">
-        <v>91</v>
+        <v>93.1</v>
       </c>
       <c r="F17" s="10">
-        <v>257492</v>
+        <v>1495223</v>
       </c>
     </row>
     <row r="18">
@@ -835,14 +853,14 @@
       <c r="C18" s="11"/>
       <c r="D18" s="10" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="E18" s="12">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="F18" s="10">
-        <v>4942</v>
+        <v>19030</v>
       </c>
     </row>
     <row r="19">
@@ -851,14 +869,14 @@
       <c r="C19" s="11"/>
       <c r="D19" s="10" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>UT</t>
         </is>
       </c>
       <c r="E19" s="12">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="F19" s="10">
-        <v>3757</v>
+        <v>16305</v>
       </c>
     </row>
     <row r="20">
@@ -867,14 +885,14 @@
       <c r="C20" s="11"/>
       <c r="D20" s="10" t="inlineStr">
         <is>
-          <t>VA</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="E20" s="12">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="F20" s="10">
-        <v>3102</v>
+        <v>14967</v>
       </c>
     </row>
     <row r="21">
@@ -883,14 +901,14 @@
       <c r="C21" s="11"/>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>NC</t>
+          <t>WA</t>
         </is>
       </c>
       <c r="E21" s="12">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="F21" s="10">
-        <v>2762</v>
+        <v>13766</v>
       </c>
     </row>
     <row r="22">
@@ -903,10 +921,10 @@
         </is>
       </c>
       <c r="E22" s="12">
-        <v>3.9</v>
+        <v>2.9</v>
       </c>
       <c r="F22" s="10">
-        <v>10992</v>
+        <v>47297</v>
       </c>
     </row>
     <row r="23">
@@ -946,10 +964,10 @@
         </is>
       </c>
       <c r="E23" s="12">
-        <v>5.5</v>
+        <v>17</v>
       </c>
       <c r="F23" s="10">
-        <v>15618</v>
+        <v>273826</v>
       </c>
     </row>
     <row r="24">
@@ -962,10 +980,10 @@
         </is>
       </c>
       <c r="E24" s="12">
-        <v>5.2</v>
+        <v>10.2</v>
       </c>
       <c r="F24" s="10">
-        <v>14579</v>
+        <v>164134</v>
       </c>
     </row>
     <row r="25">
@@ -974,14 +992,14 @@
       <c r="C25" s="11"/>
       <c r="D25" s="10" t="inlineStr">
         <is>
-          <t>CL310 - Plan Received - Closure</t>
+          <t>OP23110 - Class Determination - Class 1 Mod, No Prior Approval Required</t>
         </is>
       </c>
       <c r="E25" s="12">
-        <v>3.7</v>
+        <v>6.1</v>
       </c>
       <c r="F25" s="10">
-        <v>10363</v>
+        <v>97632</v>
       </c>
     </row>
     <row r="26">
@@ -994,10 +1012,10 @@
         </is>
       </c>
       <c r="E26" s="12">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="F26" s="10">
-        <v>9777</v>
+        <v>51357</v>
       </c>
     </row>
     <row r="27">
@@ -1010,10 +1028,10 @@
         </is>
       </c>
       <c r="E27" s="12">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="F27" s="10">
-        <v>8983</v>
+        <v>44385</v>
       </c>
     </row>
     <row r="28">
@@ -1026,10 +1044,10 @@
         </is>
       </c>
       <c r="E28" s="12">
-        <v>79</v>
+        <v>60.7</v>
       </c>
       <c r="F28" s="10">
-        <v>223727</v>
+        <v>975254</v>
       </c>
     </row>
     <row r="29">
@@ -1041,7 +1059,7 @@
               <color rgb="FF000000"/>
               <rFont val="Calibri"/>
             </rPr>
-            <t xml:space="preserve">SUBORGANIZATION_OWNER
+            <t xml:space="preserve">RESPONSIBLE_PERSON_OWNER
 </t>
           </r>
           <r>
@@ -1050,29 +1068,29 @@
               <color rgb="FF666666"/>
               <rFont val="Calibri"/>
             </rPr>
-            <t>Owner of the suborganization code.</t>
+            <t>Organization that owns the record of the person responsible for the event.</t>
           </r>
         </is>
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>77.2%
-(218464)</t>
+          <t>18.2%
+(292237)</t>
         </is>
       </c>
       <c r="C29" s="11">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="D29" s="10" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>UT</t>
         </is>
       </c>
       <c r="E29" s="12">
-        <v>2.1</v>
+        <v>11.5</v>
       </c>
       <c r="F29" s="10">
-        <v>6084</v>
+        <v>184885</v>
       </c>
     </row>
     <row r="30">
@@ -1081,14 +1099,14 @@
       <c r="C30" s="11"/>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>WA</t>
         </is>
       </c>
       <c r="E30" s="12">
-        <v>2</v>
+        <v>9.2</v>
       </c>
       <c r="F30" s="10">
-        <v>5673</v>
+        <v>148325</v>
       </c>
     </row>
     <row r="31">
@@ -1097,14 +1115,14 @@
       <c r="C31" s="11"/>
       <c r="D31" s="10" t="inlineStr">
         <is>
-          <t>VA</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="E31" s="12">
-        <v>1.9</v>
+        <v>7</v>
       </c>
       <c r="F31" s="10">
-        <v>5408</v>
+        <v>112451</v>
       </c>
     </row>
     <row r="32">
@@ -1117,10 +1135,10 @@
         </is>
       </c>
       <c r="E32" s="12">
-        <v>1.9</v>
+        <v>6.9</v>
       </c>
       <c r="F32" s="10">
-        <v>5340</v>
+        <v>110439</v>
       </c>
     </row>
     <row r="33">
@@ -1129,14 +1147,14 @@
       <c r="C33" s="11"/>
       <c r="D33" s="10" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="E33" s="12">
-        <v>1.8</v>
+        <v>5.1</v>
       </c>
       <c r="F33" s="10">
-        <v>5049</v>
+        <v>81921</v>
       </c>
     </row>
     <row r="34">
@@ -1145,14 +1163,14 @@
       <c r="C34" s="11"/>
       <c r="D34" s="10" t="inlineStr">
         <is>
-          <t>All Other (39)</t>
+          <t>All Other (54)</t>
         </is>
       </c>
       <c r="E34" s="12">
-        <v>13.1</v>
+        <v>42.1</v>
       </c>
       <c r="F34" s="10">
-        <v>37029</v>
+        <v>676330</v>
       </c>
     </row>
     <row r="35">
@@ -1164,7 +1182,7 @@
               <color rgb="FF000000"/>
               <rFont val="Calibri"/>
             </rPr>
-            <t xml:space="preserve">SUBORGANIZATION
+            <t xml:space="preserve">SUBORGANIZATION_OWNER
 </t>
           </r>
           <r>
@@ -1173,29 +1191,29 @@
               <color rgb="FF666666"/>
               <rFont val="Calibri"/>
             </rPr>
-            <t>Suborganization code assigned to the permitting event.</t>
+            <t>Organization that owns the suborganization record on the event.</t>
           </r>
         </is>
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>77.2%
-(218464)</t>
+          <t>61.4%
+(986214)</t>
         </is>
       </c>
       <c r="C35" s="11">
-        <v>155</v>
+        <v>44</v>
       </c>
       <c r="D35" s="10" t="inlineStr">
         <is>
-          <t>HW</t>
+          <t>WA</t>
         </is>
       </c>
       <c r="E35" s="12">
-        <v>3.3</v>
+        <v>9.3</v>
       </c>
       <c r="F35" s="10">
-        <v>9242</v>
+        <v>149001</v>
       </c>
     </row>
     <row r="36">
@@ -1208,10 +1226,10 @@
         </is>
       </c>
       <c r="E36" s="12">
-        <v>2.8</v>
+        <v>6.2</v>
       </c>
       <c r="F36" s="10">
-        <v>7854</v>
+        <v>100331</v>
       </c>
     </row>
     <row r="37">
@@ -1220,14 +1238,14 @@
       <c r="C37" s="11"/>
       <c r="D37" s="10" t="inlineStr">
         <is>
-          <t>NCP</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="E37" s="12">
-        <v>1.7</v>
+        <v>4.1</v>
       </c>
       <c r="F37" s="10">
-        <v>4875</v>
+        <v>65202</v>
       </c>
     </row>
     <row r="38">
@@ -1236,14 +1254,14 @@
       <c r="C38" s="11"/>
       <c r="D38" s="10" t="inlineStr">
         <is>
-          <t>SW</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="E38" s="12">
-        <v>1.7</v>
+        <v>3.6</v>
       </c>
       <c r="F38" s="10">
-        <v>4764</v>
+        <v>58545</v>
       </c>
     </row>
     <row r="39">
@@ -1252,14 +1270,14 @@
       <c r="C39" s="11"/>
       <c r="D39" s="10" t="inlineStr">
         <is>
-          <t>PMT</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="E39" s="12">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
       <c r="F39" s="10">
-        <v>4506</v>
+        <v>37590</v>
       </c>
     </row>
     <row r="40">
@@ -1268,14 +1286,14 @@
       <c r="C40" s="11"/>
       <c r="D40" s="10" t="inlineStr">
         <is>
-          <t>All Other (150)</t>
+          <t>All Other (39)</t>
         </is>
       </c>
       <c r="E40" s="12">
-        <v>11.8</v>
+        <v>13.1</v>
       </c>
       <c r="F40" s="10">
-        <v>33342</v>
+        <v>209705</v>
       </c>
     </row>
     <row r="41">
@@ -1287,7 +1305,7 @@
               <color rgb="FF000000"/>
               <rFont val="Calibri"/>
             </rPr>
-            <t xml:space="preserve">RESPONSIBLE_PERSON_OWNER
+            <t xml:space="preserve">SUBORGANIZATION
 </t>
           </r>
           <r>
@@ -1296,29 +1314,29 @@
               <color rgb="FF666666"/>
               <rFont val="Calibri"/>
             </rPr>
-            <t>Owner of the responsible-person code.</t>
+            <t>Suborganization within the implementing agency that handles the event (codes are agency-specific).</t>
           </r>
         </is>
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>28%
-(79293)</t>
+          <t>61.4%
+(986214)</t>
         </is>
       </c>
       <c r="C41" s="11">
-        <v>59</v>
+        <v>155</v>
       </c>
       <c r="D41" s="10" t="inlineStr">
         <is>
-          <t>TX</t>
+          <t>HA</t>
         </is>
       </c>
       <c r="E41" s="12">
-        <v>4.7</v>
+        <v>9.1</v>
       </c>
       <c r="F41" s="10">
-        <v>13183</v>
+        <v>145720</v>
       </c>
     </row>
     <row r="42">
@@ -1327,14 +1345,14 @@
       <c r="C42" s="11"/>
       <c r="D42" s="10" t="inlineStr">
         <is>
-          <t>NC</t>
+          <t>HW</t>
         </is>
       </c>
       <c r="E42" s="12">
-        <v>4.4</v>
+        <v>5.2</v>
       </c>
       <c r="F42" s="10">
-        <v>12451</v>
+        <v>82952</v>
       </c>
     </row>
     <row r="43">
@@ -1343,14 +1361,14 @@
       <c r="C43" s="11"/>
       <c r="D43" s="10" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>HWP</t>
         </is>
       </c>
       <c r="E43" s="12">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="F43" s="10">
-        <v>12311</v>
+        <v>64583</v>
       </c>
     </row>
     <row r="44">
@@ -1359,14 +1377,14 @@
       <c r="C44" s="11"/>
       <c r="D44" s="10" t="inlineStr">
         <is>
-          <t>OH</t>
+          <t>FES</t>
         </is>
       </c>
       <c r="E44" s="12">
-        <v>4.2</v>
+        <v>2.3</v>
       </c>
       <c r="F44" s="10">
-        <v>11897</v>
+        <v>36578</v>
       </c>
     </row>
     <row r="45">
@@ -1375,14 +1393,14 @@
       <c r="C45" s="11"/>
       <c r="D45" s="10" t="inlineStr">
         <is>
-          <t>02 - EPA Region 2</t>
+          <t>SW</t>
         </is>
       </c>
       <c r="E45" s="12">
-        <v>3.9</v>
+        <v>2.1</v>
       </c>
       <c r="F45" s="10">
-        <v>11074</v>
+        <v>33732</v>
       </c>
     </row>
     <row r="46">
@@ -1391,14 +1409,14 @@
       <c r="C46" s="11"/>
       <c r="D46" s="10" t="inlineStr">
         <is>
-          <t>All Other (54)</t>
+          <t>All Other (150)</t>
         </is>
       </c>
       <c r="E46" s="12">
-        <v>50.5</v>
+        <v>16</v>
       </c>
       <c r="F46" s="10">
-        <v>142838</v>
+        <v>256809</v>
       </c>
     </row>
     <row r="47">
@@ -1410,7 +1428,7 @@
               <color rgb="FF000000"/>
               <rFont val="Calibri"/>
             </rPr>
-            <t xml:space="preserve">RESPONSIBLE_PERSON
+            <t xml:space="preserve">SERIES_RESPONSIBLE_PERSON_OWNER
 </t>
           </r>
           <r>
@@ -1419,29 +1437,29 @@
               <color rgb="FF666666"/>
               <rFont val="Calibri"/>
             </rPr>
-            <t>Responsible-person code assigned to the permitting event.</t>
+            <t>Organization that owns the record of the person responsible for the permit series.</t>
           </r>
         </is>
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>28%
-(79293)</t>
+          <t>19.3%
+(310773)</t>
         </is>
       </c>
       <c r="C47" s="11">
-        <v>3678</v>
+        <v>51</v>
       </c>
       <c r="D47" s="10" t="inlineStr">
         <is>
-          <t>OH</t>
+          <t>UT</t>
         </is>
       </c>
       <c r="E47" s="12">
-        <v>2.1</v>
+        <v>11.8</v>
       </c>
       <c r="F47" s="10">
-        <v>5824</v>
+        <v>189724</v>
       </c>
     </row>
     <row r="48">
@@ -1450,14 +1468,14 @@
       <c r="C48" s="11"/>
       <c r="D48" s="10" t="inlineStr">
         <is>
-          <t>TX</t>
+          <t>WA</t>
         </is>
       </c>
       <c r="E48" s="12">
-        <v>2</v>
+        <v>9.5</v>
       </c>
       <c r="F48" s="10">
-        <v>5555</v>
+        <v>152597</v>
       </c>
     </row>
     <row r="49">
@@ -1466,14 +1484,14 @@
       <c r="C49" s="11"/>
       <c r="D49" s="10" t="inlineStr">
         <is>
-          <t>R9STA</t>
+          <t>CO</t>
         </is>
       </c>
       <c r="E49" s="12">
-        <v>2</v>
+        <v>7.1</v>
       </c>
       <c r="F49" s="10">
-        <v>5529</v>
+        <v>114408</v>
       </c>
     </row>
     <row r="50">
@@ -1482,14 +1500,14 @@
       <c r="C50" s="11"/>
       <c r="D50" s="10" t="inlineStr">
         <is>
-          <t>R9EPA</t>
+          <t>TN</t>
         </is>
       </c>
       <c r="E50" s="12">
-        <v>1.7</v>
+        <v>6.4</v>
       </c>
       <c r="F50" s="10">
-        <v>4741</v>
+        <v>102589</v>
       </c>
     </row>
     <row r="51">
@@ -1498,14 +1516,14 @@
       <c r="C51" s="11"/>
       <c r="D51" s="10" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="E51" s="12">
-        <v>1.3</v>
+        <v>5.4</v>
       </c>
       <c r="F51" s="10">
-        <v>3623</v>
+        <v>86321</v>
       </c>
     </row>
     <row r="52">
@@ -1514,80 +1532,1413 @@
       <c r="C52" s="11"/>
       <c r="D52" s="10" t="inlineStr">
         <is>
-          <t>All Other (3673)</t>
+          <t>All Other (46)</t>
         </is>
       </c>
       <c r="E52" s="12">
-        <v>63.1</v>
+        <v>40.5</v>
       </c>
       <c r="F52" s="10">
-        <v>178482</v>
+        <v>650176</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color rgb="FF000000"/>
+              <rFont val="Calibri"/>
+            </rPr>
+            <t xml:space="preserve">PROCESS_CODE_OWNER
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color rgb="FF666666"/>
+              <rFont val="Calibri"/>
+            </rPr>
+            <t>Organization that defines the process code list.</t>
+          </r>
+        </is>
+      </c>
+      <c r="B53" s="11" t="inlineStr">
+        <is>
+          <t>0.9%
+(14593)</t>
+        </is>
+      </c>
+      <c r="C53" s="11">
+        <v>1</v>
+      </c>
+      <c r="D53" s="10" t="inlineStr">
+        <is>
+          <t>HQ - Nationally Defined Values</t>
+        </is>
+      </c>
+      <c r="E53" s="12">
+        <v>99.1</v>
+      </c>
+      <c r="F53" s="10">
+        <v>1591995</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="14" t="inlineStr">
+      <c r="A54" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color rgb="FF000000"/>
+              <rFont val="Calibri"/>
+            </rPr>
+            <t xml:space="preserve">PROCESS_CODE
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color rgb="FF666666"/>
+              <rFont val="Calibri"/>
+            </rPr>
+            <t>Process code of the linked unit (S = storage, T = treatment, D = disposal families).</t>
+          </r>
+        </is>
+      </c>
+      <c r="B54" s="11" t="inlineStr">
+        <is>
+          <t>0.9%
+(14593)</t>
+        </is>
+      </c>
+      <c r="C54" s="11">
+        <v>34</v>
+      </c>
+      <c r="D54" s="10" t="inlineStr">
+        <is>
+          <t>S01 - Container</t>
+        </is>
+      </c>
+      <c r="E54" s="12">
+        <v>38.9</v>
+      </c>
+      <c r="F54" s="10">
+        <v>624281</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="10"/>
+      <c r="B55" s="11"/>
+      <c r="C55" s="11"/>
+      <c r="D55" s="10" t="inlineStr">
+        <is>
+          <t>S02 - Tank Storage</t>
+        </is>
+      </c>
+      <c r="E55" s="12">
+        <v>20.3</v>
+      </c>
+      <c r="F55" s="10">
+        <v>326126</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="10"/>
+      <c r="B56" s="11"/>
+      <c r="C56" s="11"/>
+      <c r="D56" s="10" t="inlineStr">
+        <is>
+          <t>T04 - Other Treatment</t>
+        </is>
+      </c>
+      <c r="E56" s="12">
+        <v>7.4</v>
+      </c>
+      <c r="F56" s="10">
+        <v>119144</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="10"/>
+      <c r="B57" s="11"/>
+      <c r="C57" s="11"/>
+      <c r="D57" s="10" t="inlineStr">
+        <is>
+          <t>D80 - Landfill</t>
+        </is>
+      </c>
+      <c r="E57" s="12">
+        <v>7.2</v>
+      </c>
+      <c r="F57" s="10">
+        <v>115011</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="10"/>
+      <c r="B58" s="11"/>
+      <c r="C58" s="11"/>
+      <c r="D58" s="10" t="inlineStr">
+        <is>
+          <t>T01 - Tank Treatment</t>
+        </is>
+      </c>
+      <c r="E58" s="12">
+        <v>6.5</v>
+      </c>
+      <c r="F58" s="10">
+        <v>104067</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="10"/>
+      <c r="B59" s="11"/>
+      <c r="C59" s="11"/>
+      <c r="D59" s="10" t="inlineStr">
+        <is>
+          <t>All Other (29)</t>
+        </is>
+      </c>
+      <c r="E59" s="12">
+        <v>18.9</v>
+      </c>
+      <c r="F59" s="10">
+        <v>303366</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color rgb="FF000000"/>
+              <rFont val="Calibri"/>
+            </rPr>
+            <t xml:space="preserve">CAPACITY_TYPE
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color rgb="FF666666"/>
+              <rFont val="Calibri"/>
+            </rPr>
+            <t>Type of the reported unit capacity (codes P, O, D).</t>
+          </r>
+        </is>
+      </c>
+      <c r="B60" s="11" t="inlineStr">
+        <is>
+          <t>28.2%
+(453490)</t>
+        </is>
+      </c>
+      <c r="C60" s="11">
+        <v>3</v>
+      </c>
+      <c r="D60" s="10" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="E60" s="12">
+        <v>41.9</v>
+      </c>
+      <c r="F60" s="10">
+        <v>673862</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="10"/>
+      <c r="B61" s="11"/>
+      <c r="C61" s="11"/>
+      <c r="D61" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E61" s="12">
+        <v>22.9</v>
+      </c>
+      <c r="F61" s="10">
+        <v>367529</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="10"/>
+      <c r="B62" s="11"/>
+      <c r="C62" s="11"/>
+      <c r="D62" s="10" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E62" s="12">
+        <v>7</v>
+      </c>
+      <c r="F62" s="10">
+        <v>111707</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color rgb="FF000000"/>
+              <rFont val="Calibri"/>
+            </rPr>
+            <t xml:space="preserve">UOM_OWNER
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color rgb="FF666666"/>
+              <rFont val="Calibri"/>
+            </rPr>
+            <t>Organization that defines the unit-of-measure code list.</t>
+          </r>
+        </is>
+      </c>
+      <c r="B63" s="11" t="inlineStr">
+        <is>
+          <t>0.9%
+(14593)</t>
+        </is>
+      </c>
+      <c r="C63" s="11">
+        <v>1</v>
+      </c>
+      <c r="D63" s="10" t="inlineStr">
+        <is>
+          <t>HQ - Nationally Defined Values</t>
+        </is>
+      </c>
+      <c r="E63" s="12">
+        <v>99.1</v>
+      </c>
+      <c r="F63" s="10">
+        <v>1591995</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color rgb="FF000000"/>
+              <rFont val="Calibri"/>
+            </rPr>
+            <t xml:space="preserve">UOM_TYPE
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color rgb="FF666666"/>
+              <rFont val="Calibri"/>
+            </rPr>
+            <t>Unit of measure the capacity is reported in.</t>
+          </r>
+        </is>
+      </c>
+      <c r="B64" s="11" t="inlineStr">
+        <is>
+          <t>0.9%
+(14593)</t>
+        </is>
+      </c>
+      <c r="C64" s="11">
+        <v>21</v>
+      </c>
+      <c r="D64" s="10" t="inlineStr">
+        <is>
+          <t>G - Gallons</t>
+        </is>
+      </c>
+      <c r="E64" s="12">
+        <v>57.8</v>
+      </c>
+      <c r="F64" s="10">
+        <v>928068</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="10"/>
+      <c r="B65" s="11"/>
+      <c r="C65" s="11"/>
+      <c r="D65" s="10" t="inlineStr">
+        <is>
+          <t>U - Gallons Per Day</t>
+        </is>
+      </c>
+      <c r="E65" s="12">
+        <v>11.2</v>
+      </c>
+      <c r="F65" s="10">
+        <v>179606</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="10"/>
+      <c r="B66" s="11"/>
+      <c r="C66" s="11"/>
+      <c r="D66" s="10" t="inlineStr">
+        <is>
+          <t>C - Cubic Meters</t>
+        </is>
+      </c>
+      <c r="E66" s="12">
+        <v>5.9</v>
+      </c>
+      <c r="F66" s="10">
+        <v>94984</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="10"/>
+      <c r="B67" s="11"/>
+      <c r="C67" s="11"/>
+      <c r="D67" s="10" t="inlineStr">
+        <is>
+          <t>Y - Cubic Yards</t>
+        </is>
+      </c>
+      <c r="E67" s="12">
+        <v>5.6</v>
+      </c>
+      <c r="F67" s="10">
+        <v>90739</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="10"/>
+      <c r="B68" s="11"/>
+      <c r="C68" s="11"/>
+      <c r="D68" s="10" t="inlineStr">
+        <is>
+          <t>D - Short Tons Per Hour</t>
+        </is>
+      </c>
+      <c r="E68" s="12">
+        <v>3.3</v>
+      </c>
+      <c r="F68" s="10">
+        <v>52542</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="10"/>
+      <c r="B69" s="11"/>
+      <c r="C69" s="11"/>
+      <c r="D69" s="10" t="inlineStr">
+        <is>
+          <t>All Other (16)</t>
+        </is>
+      </c>
+      <c r="E69" s="12">
+        <v>15.3</v>
+      </c>
+      <c r="F69" s="10">
+        <v>246056</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color rgb="FF000000"/>
+              <rFont val="Calibri"/>
+            </rPr>
+            <t xml:space="preserve">LEGAL_OPERATING_STATUS_OWNER
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color rgb="FF666666"/>
+              <rFont val="Calibri"/>
+            </rPr>
+            <t>Organization that defines the legal-operating-status code list.</t>
+          </r>
+        </is>
+      </c>
+      <c r="B70" s="11" t="inlineStr">
+        <is>
+          <t>0.9%
+(14593)</t>
+        </is>
+      </c>
+      <c r="C70" s="11">
+        <v>1</v>
+      </c>
+      <c r="D70" s="10" t="inlineStr">
+        <is>
+          <t>HQ - Nationally Defined Values</t>
+        </is>
+      </c>
+      <c r="E70" s="12">
+        <v>99.1</v>
+      </c>
+      <c r="F70" s="10">
+        <v>1591995</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color rgb="FF000000"/>
+              <rFont val="Calibri"/>
+            </rPr>
+            <t xml:space="preserve">LEGAL_OPERATING_STATUS
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color rgb="FF666666"/>
+              <rFont val="Calibri"/>
+            </rPr>
+            <t>Legal / operating status of the linked process unit.</t>
+          </r>
+        </is>
+      </c>
+      <c r="B71" s="11" t="inlineStr">
+        <is>
+          <t>0.9%
+(14593)</t>
+        </is>
+      </c>
+      <c r="C71" s="11">
+        <v>218</v>
+      </c>
+      <c r="D71" s="10" t="inlineStr">
+        <is>
+          <t>PIOP - Permitted - Operating</t>
+        </is>
+      </c>
+      <c r="E71" s="12">
+        <v>54.4</v>
+      </c>
+      <c r="F71" s="10">
+        <v>874734</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="10"/>
+      <c r="B72" s="11"/>
+      <c r="C72" s="11"/>
+      <c r="D72" s="10" t="inlineStr">
+        <is>
+          <t>PTBC - Permit Terminated - Before Construction</t>
+        </is>
+      </c>
+      <c r="E72" s="12">
+        <v>7.3</v>
+      </c>
+      <c r="F72" s="10">
+        <v>117928</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="10"/>
+      <c r="B73" s="11"/>
+      <c r="C73" s="11"/>
+      <c r="D73" s="10" t="inlineStr">
+        <is>
+          <t>ISOP - Interim Status - Operating</t>
+        </is>
+      </c>
+      <c r="E73" s="12">
+        <v>4.3</v>
+      </c>
+      <c r="F73" s="10">
+        <v>68302</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="10"/>
+      <c r="B74" s="11"/>
+      <c r="C74" s="11"/>
+      <c r="D74" s="10" t="inlineStr">
+        <is>
+          <t>PTCC - Permit Terminated - Clean Closed</t>
+        </is>
+      </c>
+      <c r="E74" s="12">
+        <v>3.4</v>
+      </c>
+      <c r="F74" s="10">
+        <v>54643</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="10"/>
+      <c r="B75" s="11"/>
+      <c r="C75" s="11"/>
+      <c r="D75" s="10" t="inlineStr">
+        <is>
+          <t>PIBC - Permitted - Before Construction</t>
+        </is>
+      </c>
+      <c r="E75" s="12">
+        <v>3.1</v>
+      </c>
+      <c r="F75" s="10">
+        <v>50377</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="10"/>
+      <c r="B76" s="11"/>
+      <c r="C76" s="11"/>
+      <c r="D76" s="10" t="inlineStr">
+        <is>
+          <t>All Other (213)</t>
+        </is>
+      </c>
+      <c r="E76" s="12">
+        <v>26.5</v>
+      </c>
+      <c r="F76" s="10">
+        <v>426011</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color rgb="FF000000"/>
+              <rFont val="Calibri"/>
+            </rPr>
+            <t xml:space="preserve">COMMERCIAL_STATUS
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color rgb="FF666666"/>
+              <rFont val="Calibri"/>
+            </rPr>
+            <t>Commercial availability of the linked process unit (codes 0-3).</t>
+          </r>
+        </is>
+      </c>
+      <c r="B77" s="11" t="inlineStr">
+        <is>
+          <t>1%
+(16339)</t>
+        </is>
+      </c>
+      <c r="C77" s="11">
+        <v>4</v>
+      </c>
+      <c r="D77" s="10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E77" s="12">
+        <v>60.8</v>
+      </c>
+      <c r="F77" s="10">
+        <v>977472</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="10"/>
+      <c r="B78" s="11"/>
+      <c r="C78" s="11"/>
+      <c r="D78" s="10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E78" s="12">
+        <v>36.4</v>
+      </c>
+      <c r="F78" s="10">
+        <v>585582</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="10"/>
+      <c r="B79" s="11"/>
+      <c r="C79" s="11"/>
+      <c r="D79" s="10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E79" s="12">
+        <v>1.1</v>
+      </c>
+      <c r="F79" s="10">
+        <v>18191</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="10"/>
+      <c r="B80" s="11"/>
+      <c r="C80" s="11"/>
+      <c r="D80" s="10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E80" s="12">
+        <v>0.6</v>
+      </c>
+      <c r="F80" s="10">
+        <v>9004</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color rgb="FF000000"/>
+              <rFont val="Calibri"/>
+            </rPr>
+            <t xml:space="preserve">WASTE_CODE_OWNER
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color rgb="FF666666"/>
+              <rFont val="Calibri"/>
+            </rPr>
+            <t>Organization that defines the waste code list.</t>
+          </r>
+        </is>
+      </c>
+      <c r="B81" s="11" t="inlineStr">
+        <is>
+          <t>64.4%
+(1034740)</t>
+        </is>
+      </c>
+      <c r="C81" s="11">
+        <v>8</v>
+      </c>
+      <c r="D81" s="10" t="inlineStr">
+        <is>
+          <t>HQ - Nationally Defined Values</t>
+        </is>
+      </c>
+      <c r="E81" s="12">
+        <v>35.3</v>
+      </c>
+      <c r="F81" s="10">
+        <v>567229</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="10"/>
+      <c r="B82" s="11"/>
+      <c r="C82" s="11"/>
+      <c r="D82" s="10" t="inlineStr">
+        <is>
+          <t>WA</t>
+        </is>
+      </c>
+      <c r="E82" s="12">
+        <v>0.2</v>
+      </c>
+      <c r="F82" s="10">
+        <v>3031</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="10"/>
+      <c r="B83" s="11"/>
+      <c r="C83" s="11"/>
+      <c r="D83" s="10" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="E83" s="12">
+        <v>0.1</v>
+      </c>
+      <c r="F83" s="10">
+        <v>1432</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="10"/>
+      <c r="B84" s="11"/>
+      <c r="C84" s="11"/>
+      <c r="D84" s="10" t="inlineStr">
+        <is>
+          <t>FL</t>
+        </is>
+      </c>
+      <c r="E84" s="12">
+        <v>0</v>
+      </c>
+      <c r="F84" s="10">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="10"/>
+      <c r="B85" s="11"/>
+      <c r="C85" s="11"/>
+      <c r="D85" s="10" t="inlineStr">
+        <is>
+          <t>NY</t>
+        </is>
+      </c>
+      <c r="E85" s="12">
+        <v>0</v>
+      </c>
+      <c r="F85" s="10">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="10"/>
+      <c r="B86" s="11"/>
+      <c r="C86" s="11"/>
+      <c r="D86" s="10" t="inlineStr">
+        <is>
+          <t>All Other (3)</t>
+        </is>
+      </c>
+      <c r="E86" s="12">
+        <v>0</v>
+      </c>
+      <c r="F86" s="10">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color rgb="FF000000"/>
+              <rFont val="Calibri"/>
+            </rPr>
+            <t xml:space="preserve">WASTE_CODE
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color rgb="FF666666"/>
+              <rFont val="Calibri"/>
+            </rPr>
+            <t>Waste code the linked unit is permitted to manage (one row per code).</t>
+          </r>
+        </is>
+      </c>
+      <c r="B87" s="11" t="inlineStr">
+        <is>
+          <t>64.4%
+(1034740)</t>
+        </is>
+      </c>
+      <c r="C87" s="11">
+        <v>601</v>
+      </c>
+      <c r="D87" s="10" t="inlineStr">
+        <is>
+          <t>D001 - Ignitable Waste</t>
+        </is>
+      </c>
+      <c r="E87" s="12">
+        <v>0.5</v>
+      </c>
+      <c r="F87" s="10">
+        <v>7864</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="10"/>
+      <c r="B88" s="11"/>
+      <c r="C88" s="11"/>
+      <c r="D88" s="10" t="inlineStr">
+        <is>
+          <t>D008 - Lead</t>
+        </is>
+      </c>
+      <c r="E88" s="12">
+        <v>0.5</v>
+      </c>
+      <c r="F88" s="10">
+        <v>7797</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="10"/>
+      <c r="B89" s="11"/>
+      <c r="C89" s="11"/>
+      <c r="D89" s="10" t="inlineStr">
+        <is>
+          <t>D007 - Chromium</t>
+        </is>
+      </c>
+      <c r="E89" s="12">
+        <v>0.5</v>
+      </c>
+      <c r="F89" s="10">
+        <v>7384</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="10"/>
+      <c r="B90" s="11"/>
+      <c r="C90" s="11"/>
+      <c r="D90" s="10" t="inlineStr">
+        <is>
+          <t>D006 - Cadmium</t>
+        </is>
+      </c>
+      <c r="E90" s="12">
+        <v>0.4</v>
+      </c>
+      <c r="F90" s="10">
+        <v>6786</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="10"/>
+      <c r="B91" s="11"/>
+      <c r="C91" s="11"/>
+      <c r="D91" s="10" t="inlineStr">
+        <is>
+          <t>D018 - Benzene</t>
+        </is>
+      </c>
+      <c r="E91" s="12">
+        <v>0.4</v>
+      </c>
+      <c r="F91" s="10">
+        <v>6020</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="10"/>
+      <c r="B92" s="11"/>
+      <c r="C92" s="11"/>
+      <c r="D92" s="10" t="inlineStr">
+        <is>
+          <t>All Other (596)</t>
+        </is>
+      </c>
+      <c r="E92" s="12">
+        <v>33.4</v>
+      </c>
+      <c r="F92" s="10">
+        <v>535997</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color rgb="FF000000"/>
+              <rFont val="Calibri"/>
+            </rPr>
+            <t xml:space="preserve">SUBSEQUENT_MOD_ACTIVITY_LOCATION
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color rgb="FF666666"/>
+              <rFont val="Calibri"/>
+            </rPr>
+            <t>State or territory responsible for the later modification event linked to this one.</t>
+          </r>
+        </is>
+      </c>
+      <c r="B93" s="11" t="inlineStr">
+        <is>
+          <t>88.9%
+(1428619)</t>
+        </is>
+      </c>
+      <c r="C93" s="11">
+        <v>45</v>
+      </c>
+      <c r="D93" s="10" t="inlineStr">
+        <is>
+          <t>MO</t>
+        </is>
+      </c>
+      <c r="E93" s="12">
+        <v>3.2</v>
+      </c>
+      <c r="F93" s="10">
+        <v>51376</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="10"/>
+      <c r="B94" s="11"/>
+      <c r="C94" s="11"/>
+      <c r="D94" s="10" t="inlineStr">
+        <is>
+          <t>WA</t>
+        </is>
+      </c>
+      <c r="E94" s="12">
+        <v>3.1</v>
+      </c>
+      <c r="F94" s="10">
+        <v>49504</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="10"/>
+      <c r="B95" s="11"/>
+      <c r="C95" s="11"/>
+      <c r="D95" s="10" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="E95" s="12">
+        <v>1.2</v>
+      </c>
+      <c r="F95" s="10">
+        <v>19084</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="10"/>
+      <c r="B96" s="11"/>
+      <c r="C96" s="11"/>
+      <c r="D96" s="10" t="inlineStr">
+        <is>
+          <t>OH</t>
+        </is>
+      </c>
+      <c r="E96" s="12">
+        <v>0.7</v>
+      </c>
+      <c r="F96" s="10">
+        <v>11961</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="10"/>
+      <c r="B97" s="11"/>
+      <c r="C97" s="11"/>
+      <c r="D97" s="10" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="E97" s="12">
+        <v>0.7</v>
+      </c>
+      <c r="F97" s="10">
+        <v>11455</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="10"/>
+      <c r="B98" s="11"/>
+      <c r="C98" s="11"/>
+      <c r="D98" s="10" t="inlineStr">
+        <is>
+          <t>All Other (40)</t>
+        </is>
+      </c>
+      <c r="E98" s="12">
+        <v>2.2</v>
+      </c>
+      <c r="F98" s="10">
+        <v>34589</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color rgb="FF000000"/>
+              <rFont val="Calibri"/>
+            </rPr>
+            <t xml:space="preserve">SUBSEQUENT_MOD_EVENT_AGENCY
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color rgb="FF666666"/>
+              <rFont val="Calibri"/>
+            </rPr>
+            <t>Agency responsible for the later modification event.</t>
+          </r>
+        </is>
+      </c>
+      <c r="B99" s="11" t="inlineStr">
+        <is>
+          <t>88.9%
+(1428619)</t>
+        </is>
+      </c>
+      <c r="C99" s="11">
+        <v>4</v>
+      </c>
+      <c r="D99" s="10" t="inlineStr">
+        <is>
+          <t>S - State</t>
+        </is>
+      </c>
+      <c r="E99" s="12">
+        <v>10.5</v>
+      </c>
+      <c r="F99" s="10">
+        <v>169234</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="10"/>
+      <c r="B100" s="11"/>
+      <c r="C100" s="11"/>
+      <c r="D100" s="10" t="inlineStr">
+        <is>
+          <t>J - Joint with State Lead</t>
+        </is>
+      </c>
+      <c r="E100" s="12">
+        <v>0.5</v>
+      </c>
+      <c r="F100" s="10">
+        <v>8500</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="10"/>
+      <c r="B101" s="11"/>
+      <c r="C101" s="11"/>
+      <c r="D101" s="10" t="inlineStr">
+        <is>
+          <t>E - EPA</t>
+        </is>
+      </c>
+      <c r="E101" s="12">
+        <v>0</v>
+      </c>
+      <c r="F101" s="10">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="10"/>
+      <c r="B102" s="11"/>
+      <c r="C102" s="11"/>
+      <c r="D102" s="10" t="inlineStr">
+        <is>
+          <t>P - Joint with EPA Lead</t>
+        </is>
+      </c>
+      <c r="E102" s="12">
+        <v>0</v>
+      </c>
+      <c r="F102" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color rgb="FF000000"/>
+              <rFont val="Calibri"/>
+            </rPr>
+            <t xml:space="preserve">SUBSEQUENT_MOD_EVENT_OWNER
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color rgb="FF666666"/>
+              <rFont val="Calibri"/>
+            </rPr>
+            <t>Organization that owns the later modification event record.</t>
+          </r>
+        </is>
+      </c>
+      <c r="B103" s="11" t="inlineStr">
+        <is>
+          <t>88.9%
+(1428619)</t>
+        </is>
+      </c>
+      <c r="C103" s="11">
+        <v>2</v>
+      </c>
+      <c r="D103" s="10" t="inlineStr">
+        <is>
+          <t>HQ - Nationally Defined Values</t>
+        </is>
+      </c>
+      <c r="E103" s="12">
+        <v>11.1</v>
+      </c>
+      <c r="F103" s="10">
+        <v>177959</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="10"/>
+      <c r="B104" s="11"/>
+      <c r="C104" s="11"/>
+      <c r="D104" s="10" t="inlineStr">
+        <is>
+          <t>ND</t>
+        </is>
+      </c>
+      <c r="E104" s="12">
+        <v>0</v>
+      </c>
+      <c r="F104" s="10">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color rgb="FF000000"/>
+              <rFont val="Calibri"/>
+            </rPr>
+            <t xml:space="preserve">SUBSEQUENT_MOD_EVENT_CODE
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color rgb="FF666666"/>
+              <rFont val="Calibri"/>
+            </rPr>
+            <t>Event code of the later modification linked to this event.</t>
+          </r>
+        </is>
+      </c>
+      <c r="B105" s="11" t="inlineStr">
+        <is>
+          <t>88.9%
+(1428619)</t>
+        </is>
+      </c>
+      <c r="C105" s="11">
+        <v>56</v>
+      </c>
+      <c r="D105" s="10" t="inlineStr">
+        <is>
+          <t>OP240OH - Modification Approved - Other Modification</t>
+        </is>
+      </c>
+      <c r="E105" s="12">
+        <v>3.5</v>
+      </c>
+      <c r="F105" s="10">
+        <v>56518</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="10"/>
+      <c r="B106" s="11"/>
+      <c r="C106" s="11"/>
+      <c r="D106" s="10" t="inlineStr">
+        <is>
+          <t>OP236AP - Modification Public Notice - Intent to Approve</t>
+        </is>
+      </c>
+      <c r="E106" s="12">
+        <v>1.7</v>
+      </c>
+      <c r="F106" s="10">
+        <v>26698</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="10"/>
+      <c r="B107" s="11"/>
+      <c r="C107" s="11"/>
+      <c r="D107" s="10" t="inlineStr">
+        <is>
+          <t>OP23110 - Class Determination - Class 1 Mod, No Prior Approval Required</t>
+        </is>
+      </c>
+      <c r="E107" s="12">
+        <v>1.5</v>
+      </c>
+      <c r="F107" s="10">
+        <v>24499</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="10"/>
+      <c r="B108" s="11"/>
+      <c r="C108" s="11"/>
+      <c r="D108" s="10" t="inlineStr">
+        <is>
+          <t>OP241 - Final Modification Effective Date</t>
+        </is>
+      </c>
+      <c r="E108" s="12">
+        <v>1.2</v>
+      </c>
+      <c r="F108" s="10">
+        <v>19895</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="10"/>
+      <c r="B109" s="11"/>
+      <c r="C109" s="11"/>
+      <c r="D109" s="10" t="inlineStr">
+        <is>
+          <t>OP23111 - Class Determination - Class 1 Mod, Prior Approval Required</t>
+        </is>
+      </c>
+      <c r="E109" s="12">
+        <v>0.6</v>
+      </c>
+      <c r="F109" s="10">
+        <v>10266</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="10"/>
+      <c r="B110" s="11"/>
+      <c r="C110" s="11"/>
+      <c r="D110" s="10" t="inlineStr">
+        <is>
+          <t>All Other (51)</t>
+        </is>
+      </c>
+      <c r="E110" s="12">
+        <v>2.5</v>
+      </c>
+      <c r="F110" s="10">
+        <v>40093</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="14" t="inlineStr">
         <is>
           <t>Notes on missing values:
-SUBORGANIZATION / SUBORGANIZATION_OWNER: Not determinable.
-RESPONSIBLE_PERSON / RESPONSIBLE_PERSON_OWNER: Not determinable.</t>
-        </is>
-      </c>
-      <c r="B54" s="14"/>
-      <c r="C54" s="14"/>
-      <c r="D54" s="14"/>
-      <c r="E54" s="14"/>
-      <c r="F54" s="14"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="14"/>
-      <c r="B55" s="14"/>
-      <c r="C55" s="14"/>
-      <c r="D55" s="14"/>
-      <c r="E55" s="14"/>
-      <c r="F55" s="14"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="14"/>
-      <c r="B56" s="14"/>
-      <c r="C56" s="14"/>
-      <c r="D56" s="14"/>
-      <c r="E56" s="14"/>
-      <c r="F56" s="14"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="14" t="inlineStr">
+SUBORGANIZATION_OWNER / SUBORGANIZATION: Missing. Only the agencies that record a handling suborganization fill these.
+PROCESS_CODE / LEGAL_OPERATING_STATUS / COMMERCIAL_STATUS / CAPACITY_TYPE / UOM_TYPE and their owner columns: Not applicable. Blank on events with no linked unit detail.
+WASTE_CODE_OWNER / WASTE_CODE: Not applicable. Only the unit details that list permitted waste codes carry these.
+SUBSEQUENT_MOD_*: Not applicable. Only the events that a later modification points back to carry a link.</t>
+        </is>
+      </c>
+      <c r="B112" s="14"/>
+      <c r="C112" s="14"/>
+      <c r="D112" s="14"/>
+      <c r="E112" s="14"/>
+      <c r="F112" s="14"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="14"/>
+      <c r="B113" s="14"/>
+      <c r="C113" s="14"/>
+      <c r="D113" s="14"/>
+      <c r="E113" s="14"/>
+      <c r="F113" s="14"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="14"/>
+      <c r="B114" s="14"/>
+      <c r="C114" s="14"/>
+      <c r="D114" s="14"/>
+      <c r="E114" s="14"/>
+      <c r="F114" s="14"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="14"/>
+      <c r="B115" s="14"/>
+      <c r="C115" s="14"/>
+      <c r="D115" s="14"/>
+      <c r="E115" s="14"/>
+      <c r="F115" s="14"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="14"/>
+      <c r="B116" s="14"/>
+      <c r="C116" s="14"/>
+      <c r="D116" s="14"/>
+      <c r="E116" s="14"/>
+      <c r="F116" s="14"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="14" t="inlineStr">
         <is>
           <t>Variables dropped (present in the source file but not summarized):
-'SERIES_SEQ', 'EVENT_SEQ'</t>
-        </is>
-      </c>
-      <c r="B58" s="14"/>
-      <c r="C58" s="14"/>
-      <c r="D58" s="14"/>
-      <c r="E58" s="14"/>
-      <c r="F58" s="14"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="14"/>
-      <c r="B59" s="14"/>
-      <c r="C59" s="14"/>
-      <c r="D59" s="14"/>
-      <c r="E59" s="14"/>
-      <c r="F59" s="14"/>
+'RESPONSIBLE_PERSON', 'SERIES_NAME', 'SERIES_RESPONSIBLE_PERSON',
+'UNIT_DETAIL_HANDLER_ID', 'UNIT_NAME', 'SUBSEQUENT_MOD_HANDLER_ID'</t>
+        </is>
+      </c>
+      <c r="B118" s="14"/>
+      <c r="C118" s="14"/>
+      <c r="D118" s="14"/>
+      <c r="E118" s="14"/>
+      <c r="F118" s="14"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="14"/>
+      <c r="B119" s="14"/>
+      <c r="C119" s="14"/>
+      <c r="D119" s="14"/>
+      <c r="E119" s="14"/>
+      <c r="F119" s="14"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="14"/>
+      <c r="B120" s="14"/>
+      <c r="C120" s="14"/>
+      <c r="D120" s="14"/>
+      <c r="E120" s="14"/>
+      <c r="F120" s="14"/>
     </row>
   </sheetData>
-  <mergeCells count="31">
+  <mergeCells count="64">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="C3:C4"/>
     <mergeCell ref="D3:F4"/>
     <mergeCell ref="B5:F5"/>
-    <mergeCell ref="A7:A10"/>
-    <mergeCell ref="B7:B10"/>
-    <mergeCell ref="C7:C10"/>
-    <mergeCell ref="A11:A16"/>
-    <mergeCell ref="B11:B16"/>
-    <mergeCell ref="C11:C16"/>
+    <mergeCell ref="A7:A12"/>
+    <mergeCell ref="B7:B12"/>
+    <mergeCell ref="C7:C12"/>
+    <mergeCell ref="A13:A16"/>
+    <mergeCell ref="B13:B16"/>
+    <mergeCell ref="C13:C16"/>
     <mergeCell ref="A17:A22"/>
     <mergeCell ref="B17:B22"/>
     <mergeCell ref="C17:C22"/>
@@ -1606,8 +2957,41 @@
     <mergeCell ref="A47:A52"/>
     <mergeCell ref="B47:B52"/>
     <mergeCell ref="C47:C52"/>
-    <mergeCell ref="A54:F56"/>
-    <mergeCell ref="A58:F59"/>
+    <mergeCell ref="A54:A59"/>
+    <mergeCell ref="B54:B59"/>
+    <mergeCell ref="C54:C59"/>
+    <mergeCell ref="A60:A62"/>
+    <mergeCell ref="B60:B62"/>
+    <mergeCell ref="C60:C62"/>
+    <mergeCell ref="A64:A69"/>
+    <mergeCell ref="B64:B69"/>
+    <mergeCell ref="C64:C69"/>
+    <mergeCell ref="A71:A76"/>
+    <mergeCell ref="B71:B76"/>
+    <mergeCell ref="C71:C76"/>
+    <mergeCell ref="A77:A80"/>
+    <mergeCell ref="B77:B80"/>
+    <mergeCell ref="C77:C80"/>
+    <mergeCell ref="A81:A86"/>
+    <mergeCell ref="B81:B86"/>
+    <mergeCell ref="C81:C86"/>
+    <mergeCell ref="A87:A92"/>
+    <mergeCell ref="B87:B92"/>
+    <mergeCell ref="C87:C92"/>
+    <mergeCell ref="A93:A98"/>
+    <mergeCell ref="B93:B98"/>
+    <mergeCell ref="C93:C98"/>
+    <mergeCell ref="A99:A102"/>
+    <mergeCell ref="B99:B102"/>
+    <mergeCell ref="C99:C102"/>
+    <mergeCell ref="A103:A104"/>
+    <mergeCell ref="B103:B104"/>
+    <mergeCell ref="C103:C104"/>
+    <mergeCell ref="A105:A110"/>
+    <mergeCell ref="B105:B110"/>
+    <mergeCell ref="C105:C110"/>
+    <mergeCell ref="A112:F116"/>
+    <mergeCell ref="A118:F120"/>
   </mergeCells>
   <printOptions gridLines="1" gridLinesSet="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1617,7 +3001,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="23"/>
@@ -1625,37 +3009,37 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="20" t="inlineStr">
+      <c r="A1" s="21" t="inlineStr">
         <is>
           <t>Variables</t>
         </is>
       </c>
-      <c r="B1" s="20" t="inlineStr">
+      <c r="B1" s="21" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="C1" s="20" t="inlineStr">
+      <c r="C1" s="21" t="inlineStr">
         <is>
           <t>% Missing</t>
         </is>
       </c>
-      <c r="D1" s="20" t="inlineStr">
+      <c r="D1" s="21" t="inlineStr">
         <is>
           <t>Min</t>
         </is>
       </c>
-      <c r="E1" s="20" t="inlineStr">
+      <c r="E1" s="21" t="inlineStr">
         <is>
           <t>P5</t>
         </is>
       </c>
-      <c r="F1" s="20" t="inlineStr">
+      <c r="F1" s="21" t="inlineStr">
         <is>
           <t>P95</t>
         </is>
       </c>
-      <c r="G1" s="20" t="inlineStr">
+      <c r="G1" s="21" t="inlineStr">
         <is>
           <t>Max</t>
         </is>
@@ -1668,21 +3052,21 @@
         </is>
       </c>
       <c r="B2" s="10">
-        <v>274879</v>
+        <v>1569574</v>
       </c>
       <c r="C2" s="10">
-        <v>2.9</v>
-      </c>
-      <c r="D2" s="21">
+        <v>2.3</v>
+      </c>
+      <c r="D2" s="22">
         <v>29231</v>
       </c>
-      <c r="E2" s="21">
-        <v>30544</v>
-      </c>
-      <c r="F2" s="21">
-        <v>44425</v>
-      </c>
-      <c r="G2" s="21">
+      <c r="E2" s="22">
+        <v>31490</v>
+      </c>
+      <c r="F2" s="22">
+        <v>45825</v>
+      </c>
+      <c r="G2" s="22">
         <v>47756</v>
       </c>
     </row>
@@ -1693,21 +3077,21 @@
         </is>
       </c>
       <c r="B3" s="10">
-        <v>29881</v>
+        <v>178134</v>
       </c>
       <c r="C3" s="10">
-        <v>89.4</v>
-      </c>
-      <c r="D3" s="21">
+        <v>88.9</v>
+      </c>
+      <c r="D3" s="22">
         <v>29484</v>
       </c>
-      <c r="E3" s="21">
-        <v>30526</v>
-      </c>
-      <c r="F3" s="21">
-        <v>45905</v>
-      </c>
-      <c r="G3" s="21">
+      <c r="E3" s="22">
+        <v>31115</v>
+      </c>
+      <c r="F3" s="22">
+        <v>46532</v>
+      </c>
+      <c r="G3" s="22">
         <v>2739691</v>
       </c>
     </row>
@@ -1718,21 +3102,21 @@
         </is>
       </c>
       <c r="B4" s="10">
-        <v>16287</v>
+        <v>62621</v>
       </c>
       <c r="C4" s="10">
-        <v>94.2</v>
-      </c>
-      <c r="D4" s="21">
+        <v>96.1</v>
+      </c>
+      <c r="D4" s="22">
         <v>29484</v>
       </c>
-      <c r="E4" s="21">
-        <v>30361</v>
-      </c>
-      <c r="F4" s="21">
-        <v>38624</v>
-      </c>
-      <c r="G4" s="21">
+      <c r="E4" s="22">
+        <v>30532</v>
+      </c>
+      <c r="F4" s="22">
+        <v>42592</v>
+      </c>
+      <c r="G4" s="22">
         <v>2958447</v>
       </c>
     </row>
@@ -1743,60 +3127,462 @@
         </is>
       </c>
       <c r="B5" s="10">
-        <v>283039</v>
+        <v>1606536</v>
       </c>
       <c r="C5" s="10">
         <v>0</v>
       </c>
-      <c r="D5" s="21">
+      <c r="D5" s="22">
         <v>29231</v>
       </c>
-      <c r="E5" s="21">
-        <v>30547</v>
-      </c>
-      <c r="F5" s="21">
-        <v>44601</v>
-      </c>
-      <c r="G5" s="21">
+      <c r="E5" s="22">
+        <v>31483</v>
+      </c>
+      <c r="F5" s="22">
+        <v>45838</v>
+      </c>
+      <c r="G5" s="22">
         <v>55384</v>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>EFFECTIVE_DATE</t>
+        </is>
+      </c>
+      <c r="B6" s="10">
+        <v>1591923</v>
+      </c>
+      <c r="C6" s="10">
+        <v>0.9</v>
+      </c>
+      <c r="D6" s="24" t="inlineStr">
+        <is>
+          <t>0001-03-20</t>
+        </is>
+      </c>
+      <c r="E6" s="22">
+        <v>30600</v>
+      </c>
+      <c r="F6" s="22">
+        <v>45560</v>
+      </c>
+      <c r="G6" s="22">
+        <v>46190</v>
+      </c>
+    </row>
     <row r="7">
-      <c r="A7" s="14" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>SERIES_SEQ</t>
+        </is>
+      </c>
+      <c r="B7" s="10">
+        <v>1606588</v>
+      </c>
+      <c r="C7" s="10">
+        <v>0</v>
+      </c>
+      <c r="D7" s="10">
+        <v>1</v>
+      </c>
+      <c r="E7" s="10">
+        <v>1</v>
+      </c>
+      <c r="F7" s="10">
+        <v>1009</v>
+      </c>
+      <c r="G7" s="10">
+        <v>1941</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>EVENT_SEQ</t>
+        </is>
+      </c>
+      <c r="B8" s="10">
+        <v>1606588</v>
+      </c>
+      <c r="C8" s="10">
+        <v>0</v>
+      </c>
+      <c r="D8" s="10">
+        <v>1</v>
+      </c>
+      <c r="E8" s="10">
+        <v>1</v>
+      </c>
+      <c r="F8" s="10">
+        <v>269</v>
+      </c>
+      <c r="G8" s="10">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>UNIT_SEQ</t>
+        </is>
+      </c>
+      <c r="B9" s="10">
+        <v>1591995</v>
+      </c>
+      <c r="C9" s="10">
+        <v>0.9</v>
+      </c>
+      <c r="D9" s="10">
+        <v>1</v>
+      </c>
+      <c r="E9" s="10">
+        <v>1</v>
+      </c>
+      <c r="F9" s="10">
+        <v>171</v>
+      </c>
+      <c r="G9" s="10">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>UNIT_DETAIL_SEQ</t>
+        </is>
+      </c>
+      <c r="B10" s="10">
+        <v>1591995</v>
+      </c>
+      <c r="C10" s="10">
+        <v>0.9</v>
+      </c>
+      <c r="D10" s="10">
+        <v>1</v>
+      </c>
+      <c r="E10" s="10">
+        <v>1</v>
+      </c>
+      <c r="F10" s="10">
+        <v>5</v>
+      </c>
+      <c r="G10" s="10">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>CAPACITY</t>
+        </is>
+      </c>
+      <c r="B11" s="10">
+        <v>1591995</v>
+      </c>
+      <c r="C11" s="10">
+        <v>0.9</v>
+      </c>
+      <c r="D11" s="10">
+        <v>0</v>
+      </c>
+      <c r="E11" s="10">
+        <v>1</v>
+      </c>
+      <c r="F11" s="10">
+        <v>2263583</v>
+      </c>
+      <c r="G11" s="10">
+        <v>400410000000</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>NUMBER_OF_UNITS</t>
+        </is>
+      </c>
+      <c r="B12" s="10">
+        <v>1591995</v>
+      </c>
+      <c r="C12" s="10">
+        <v>0.9</v>
+      </c>
+      <c r="D12" s="10">
+        <v>0</v>
+      </c>
+      <c r="E12" s="10">
+        <v>1</v>
+      </c>
+      <c r="F12" s="10">
+        <v>6</v>
+      </c>
+      <c r="G12" s="10">
+        <v>11000</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>SUBSEQUENT_MOD_SERIES_SEQ</t>
+        </is>
+      </c>
+      <c r="B13" s="10">
+        <v>177969</v>
+      </c>
+      <c r="C13" s="10">
+        <v>88.9</v>
+      </c>
+      <c r="D13" s="10">
+        <v>1</v>
+      </c>
+      <c r="E13" s="10">
+        <v>5</v>
+      </c>
+      <c r="F13" s="10">
+        <v>1015</v>
+      </c>
+      <c r="G13" s="10">
+        <v>1923</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>SUBSEQUENT_MOD_EVENT_SEQ</t>
+        </is>
+      </c>
+      <c r="B14" s="10">
+        <v>177969</v>
+      </c>
+      <c r="C14" s="10">
+        <v>88.9</v>
+      </c>
+      <c r="D14" s="10">
+        <v>1</v>
+      </c>
+      <c r="E14" s="10">
+        <v>1</v>
+      </c>
+      <c r="F14" s="10">
+        <v>316</v>
+      </c>
+      <c r="G14" s="10">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="14" t="inlineStr">
         <is>
           <t>Notes on missing values:
 SCHEDULE_DATE_ORIG: Not applicable. Most events are recorded as completed actuals. Only scheduled events carry a scheduled date.
-SCHEDULE_DATE_NEW: Not applicable. Only rescheduled events have a revised date.</t>
-        </is>
-      </c>
-      <c r="B7" s="14"/>
-      <c r="C7" s="14"/>
-      <c r="D7" s="14"/>
-      <c r="E7" s="14"/>
-      <c r="F7" s="14"/>
-      <c r="G7" s="14"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="14"/>
-      <c r="B8" s="14"/>
-      <c r="C8" s="14"/>
-      <c r="D8" s="14"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="14"/>
-      <c r="G8" s="14"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="14"/>
-      <c r="B9" s="14"/>
-      <c r="C9" s="14"/>
-      <c r="D9" s="14"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="14"/>
-      <c r="G9" s="14"/>
+SCHEDULE_DATE_NEW: Not applicable. Only rescheduled events have a revised date.
+EFFECTIVE_DATE / CAPACITY / NUMBER_OF_UNITS / UNIT_SEQ / UNIT_DETAIL_SEQ: Not applicable. Blank on events with no linked unit detail.
+SUBSEQUENT_MOD_SERIES_SEQ / SUBSEQUENT_MOD_EVENT_SEQ: Not applicable. Only the events that a later modification points back to carry a link.</t>
+        </is>
+      </c>
+      <c r="B16" s="14"/>
+      <c r="C16" s="14"/>
+      <c r="D16" s="14"/>
+      <c r="E16" s="14"/>
+      <c r="F16" s="14"/>
+      <c r="G16" s="14"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="14"/>
+      <c r="B17" s="14"/>
+      <c r="C17" s="14"/>
+      <c r="D17" s="14"/>
+      <c r="E17" s="14"/>
+      <c r="F17" s="14"/>
+      <c r="G17" s="14"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="14"/>
+      <c r="B18" s="14"/>
+      <c r="C18" s="14"/>
+      <c r="D18" s="14"/>
+      <c r="E18" s="14"/>
+      <c r="F18" s="14"/>
+      <c r="G18" s="14"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="14"/>
+      <c r="B19" s="14"/>
+      <c r="C19" s="14"/>
+      <c r="D19" s="14"/>
+      <c r="E19" s="14"/>
+      <c r="F19" s="14"/>
+      <c r="G19" s="14"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="14"/>
+      <c r="B20" s="14"/>
+      <c r="C20" s="14"/>
+      <c r="D20" s="14"/>
+      <c r="E20" s="14"/>
+      <c r="F20" s="14"/>
+      <c r="G20" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A7:G9"/>
+    <mergeCell ref="A16:G20"/>
+  </mergeCells>
+  <printOptions gridLines="1" gridLinesSet="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1:I6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="28.5"/>
+    <col min="2" max="9" bestFit="1" customWidth="1" hidden="false" width="12.664"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="26" t="inlineStr">
+        <is>
+          <t>Variables</t>
+        </is>
+      </c>
+      <c r="B1" s="26" t="inlineStr">
+        <is>
+          <t>N Missing</t>
+        </is>
+      </c>
+      <c r="C1" s="26" t="inlineStr">
+        <is>
+          <t>% Missing</t>
+        </is>
+      </c>
+      <c r="D1" s="26" t="inlineStr">
+        <is>
+          <t>Yes N</t>
+        </is>
+      </c>
+      <c r="E1" s="26" t="inlineStr">
+        <is>
+          <t>Yes %</t>
+        </is>
+      </c>
+      <c r="F1" s="26" t="inlineStr">
+        <is>
+          <t>No N</t>
+        </is>
+      </c>
+      <c r="G1" s="26" t="inlineStr">
+        <is>
+          <t>No %</t>
+        </is>
+      </c>
+      <c r="H1" s="26" t="inlineStr">
+        <is>
+          <t>Unknown N</t>
+        </is>
+      </c>
+      <c r="I1" s="26" t="inlineStr">
+        <is>
+          <t>Unknown %</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>STANDARDIZED_PERMIT_IND</t>
+        </is>
+      </c>
+      <c r="B2" s="10">
+        <v>14593</v>
+      </c>
+      <c r="C2" s="10">
+        <v>0.91</v>
+      </c>
+      <c r="D2" s="10">
+        <v>27272</v>
+      </c>
+      <c r="E2" s="10">
+        <v>1.7</v>
+      </c>
+      <c r="F2" s="10">
+        <v>1564723</v>
+      </c>
+      <c r="G2" s="10">
+        <v>97.39</v>
+      </c>
+      <c r="H2" s="10">
+        <v>0</v>
+      </c>
+      <c r="I2" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="10" t="inlineStr">
+        <is>
+          <t>CURRENT_UNIT_DETAIL</t>
+        </is>
+      </c>
+      <c r="B3" s="10">
+        <v>14593</v>
+      </c>
+      <c r="C3" s="10">
+        <v>0.91</v>
+      </c>
+      <c r="D3" s="10">
+        <v>1055830</v>
+      </c>
+      <c r="E3" s="10">
+        <v>65.72</v>
+      </c>
+      <c r="F3" s="10">
+        <v>536165</v>
+      </c>
+      <c r="G3" s="10">
+        <v>33.37</v>
+      </c>
+      <c r="H3" s="10">
+        <v>0</v>
+      </c>
+      <c r="I3" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="14" t="inlineStr">
+        <is>
+          <t>Notes on missing values:
+Both indicators: Missing. Blank on events with no linked unit detail.</t>
+        </is>
+      </c>
+      <c r="B5" s="14"/>
+      <c r="C5" s="14"/>
+      <c r="D5" s="14"/>
+      <c r="E5" s="14"/>
+      <c r="F5" s="14"/>
+      <c r="G5" s="14"/>
+      <c r="H5" s="14"/>
+      <c r="I5" s="14"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="14"/>
+      <c r="B6" s="14"/>
+      <c r="C6" s="14"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="14"/>
+      <c r="F6" s="14"/>
+      <c r="G6" s="14"/>
+      <c r="H6" s="14"/>
+      <c r="I6" s="14"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A5:I6"/>
   </mergeCells>
   <printOptions gridLines="1" gridLinesSet="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
